--- a/quizzes/006_gallbladder_anatomy_quiz--quizzes.xlsx
+++ b/quizzes/006_gallbladder_anatomy_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Gallbladder</t>
+          <t>Gallbladder Anatomy Quiz Form Section 17</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bile</t>
+          <t>Gallbladder Anatomy Quiz Form Section 21</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Gallstones</t>
+          <t>Gallbladder Anatomy Quiz Form Section 22</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ulcer</t>
+          <t>Gallbladder Anatomy Quiz Form Section 24</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1364,17 +1364,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>gallbladder_anatomy_quiz_form_section_6_choices</t>
+          <t>gallbladder_anatomy_quiz_form_section_7_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>bile_duct</t>
+          <t>gallstones</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bile Duct</t>
+          <t>Gallstones</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>gallstones</t>
+          <t>cholangitis</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Gallstones</t>
+          <t>Cholangitis</t>
         </is>
       </c>
     </row>
@@ -1403,29 +1403,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>cholangitis</t>
+          <t>hydrops</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cholangitis</t>
+          <t>Hydrops</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>gallbladder_anatomy_quiz_form_section_7_choices</t>
+          <t>gallbladder_anatomy_quiz_form_section_8_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hydrops</t>
+          <t>cholangitis</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hydrops</t>
+          <t>Cholangitis</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>cholangitis</t>
+          <t>inflammation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cholangitis</t>
+          <t>Inflammation</t>
         </is>
       </c>
     </row>
@@ -1454,19 +1454,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>inflammation</t>
+          <t>ulcer</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Inflammation</t>
+          <t>Ulcer</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>gallbladder_anatomy_quiz_form_section_8_choices</t>
+          <t>gallbladder_anatomy_quiz_form_section_9_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ulcer</t>
+          <t>abscess</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ulcer</t>
+          <t>Abscess</t>
         </is>
       </c>
     </row>
@@ -1505,19 +1505,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>abscess</t>
+          <t>stricture</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Abscess</t>
+          <t>Stricture</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>gallbladder_anatomy_quiz_form_section_9_choices</t>
+          <t>gallbladder_anatomy_quiz_form_section_10_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>stricture</t>
+          <t>obstruction</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Stricture</t>
+          <t>Obstruction</t>
         </is>
       </c>
     </row>
@@ -1556,29 +1556,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>obstruction</t>
+          <t>blockage</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Obstruction</t>
+          <t>Blockage</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gallbladder_anatomy_quiz_form_section_10_choices</t>
+          <t>gallbladder_anatomy_quiz_form_section_11_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>blockage</t>
+          <t>obstruction</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Blockage</t>
+          <t>Obstruction</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>obstruction</t>
+          <t>impaction</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Obstruction</t>
+          <t>Impaction</t>
         </is>
       </c>
     </row>
@@ -1607,29 +1607,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>impaction</t>
+          <t>inflammation</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Impaction</t>
+          <t>Inflammation</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>gallbladder_anatomy_quiz_form_section_11_choices</t>
+          <t>gallbladder_anatomy_quiz_form_section_12_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>inflammation</t>
+          <t>impaction</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Inflammation</t>
+          <t>Impaction</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>impaction</t>
+          <t>sphincter</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Impaction</t>
+          <t>Sphincter</t>
         </is>
       </c>
     </row>
@@ -1658,29 +1658,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>sphincter</t>
+          <t>stenosis</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sphincter</t>
+          <t>Stenosis</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>gallbladder_anatomy_quiz_form_section_12_choices</t>
+          <t>gallbladder_anatomy_quiz_form_section_13_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>stenosis</t>
+          <t>sphincter</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Stenosis</t>
+          <t>Sphincter</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>sphincter</t>
+          <t>ampulla</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sphincter</t>
+          <t>Ampulla</t>
         </is>
       </c>
     </row>
@@ -1709,19 +1709,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ampulla</t>
+          <t>common_duct</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ampulla</t>
+          <t>Common Duct</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>gallbladder_anatomy_quiz_form_section_13_choices</t>
+          <t>gallbladder_anatomy_quiz_form_section_14_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>common_duct</t>
+          <t>duct</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Common Duct</t>
+          <t>Duct</t>
         </is>
       </c>
     </row>
@@ -1760,29 +1760,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>duct</t>
+          <t>duct_system</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Duct</t>
+          <t>Duct System</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>gallbladder_anatomy_quiz_form_section_14_choices</t>
+          <t>gallbladder_anatomy_quiz_form_section_15_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>duct_system</t>
+          <t>duct</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Duct System</t>
+          <t>Duct</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>duct</t>
+          <t>duct_system</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Duct</t>
+          <t>Duct System</t>
         </is>
       </c>
     </row>
@@ -1811,19 +1811,19 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>duct_system</t>
+          <t>system</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Duct System</t>
+          <t>System</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>gallbladder_anatomy_quiz_form_section_15_choices</t>
+          <t>gallbladder_anatomy_quiz_form_section_16_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1845,46 +1845,46 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>system</t>
+          <t>systemic</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Systemic</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>gallbladder_anatomy_quiz_form_section_16_choices</t>
+          <t>gallbladder_anatomy_quiz_form_section_17_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>systemic</t>
+          <t>gallbladder</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Systemic</t>
+          <t>Gallbladder</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>gallbladder_anatomy_quiz_form_section_16_choices</t>
+          <t>gallbladder_anatomy_quiz_form_section_17_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>systemic</t>
+          <t>hepatobiliary</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Systemic</t>
+          <t>Hepatobiliary</t>
         </is>
       </c>
     </row>
@@ -1896,19 +1896,19 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>gallbladder</t>
+          <t>hepatic</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Gallbladder</t>
+          <t>Hepatic</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>gallbladder_anatomy_quiz_form_section_17_choices</t>
+          <t>gallbladder_anatomy_quiz_form_section_18_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1925,7 +1925,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>gallbladder_anatomy_quiz_form_section_17_choices</t>
+          <t>gallbladder_anatomy_quiz_form_section_18_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1947,19 +1947,19 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>hepatobiliary</t>
+          <t>biliary</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hepatobiliary</t>
+          <t>Biliary</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>gallbladder_anatomy_quiz_form_section_18_choices</t>
+          <t>gallbladder_anatomy_quiz_form_section_19_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1976,7 +1976,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>gallbladder_anatomy_quiz_form_section_18_choices</t>
+          <t>gallbladder_anatomy_quiz_form_section_19_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1998,19 +1998,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>hepatic</t>
+          <t>bile</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hepatic</t>
+          <t>Bile</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>gallbladder_anatomy_quiz_form_section_19_choices</t>
+          <t>gallbladder_anatomy_quiz_form_section_20_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2027,17 +2027,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>gallbladder_anatomy_quiz_form_section_19_choices</t>
+          <t>gallbladder_anatomy_quiz_form_section_20_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>bile</t>
+          <t>hepatic</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bile</t>
+          <t>Hepatic</t>
         </is>
       </c>
     </row>
@@ -2049,46 +2049,46 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>biliary</t>
+          <t>bile_duct</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Biliary</t>
+          <t>Bile Duct</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>gallbladder_anatomy_quiz_form_section_20_choices</t>
+          <t>gallbladder_anatomy_quiz_form_section_21_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>hepatic</t>
+          <t>bile</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hepatic</t>
+          <t>Bile</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>gallbladder_anatomy_quiz_form_section_20_choices</t>
+          <t>gallbladder_anatomy_quiz_form_section_21_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>bile_duct</t>
+          <t>gallstones</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bile Duct</t>
+          <t>Gallstones</t>
         </is>
       </c>
     </row>
@@ -2100,19 +2100,19 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>bile</t>
+          <t>gallbladder</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bile</t>
+          <t>Gallbladder</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>gallbladder_anatomy_quiz_form_section_21_choices</t>
+          <t>gallbladder_anatomy_quiz_form_section_22_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2129,17 +2129,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>gallbladder_anatomy_quiz_form_section_21_choices</t>
+          <t>gallbladder_anatomy_quiz_form_section_22_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>gallbladder</t>
+          <t>cholecystitis</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Gallbladder</t>
+          <t>Cholecystitis</t>
         </is>
       </c>
     </row>
@@ -2151,19 +2151,19 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>gallstones</t>
+          <t>inflammation</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Gallstones</t>
+          <t>Inflammation</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>gallbladder_anatomy_quiz_form_section_22_choices</t>
+          <t>gallbladder_anatomy_quiz_form_section_23_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2180,17 +2180,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>gallbladder_anatomy_quiz_form_section_22_choices</t>
+          <t>gallbladder_anatomy_quiz_form_section_23_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>inflammation</t>
+          <t>ulcer</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Inflammation</t>
+          <t>Ulcer</t>
         </is>
       </c>
     </row>
@@ -2202,19 +2202,19 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>cholecystitis</t>
+          <t>stricture</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cholecystitis</t>
+          <t>Stricture</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>gallbladder_anatomy_quiz_form_section_23_choices</t>
+          <t>gallbladder_anatomy_quiz_form_section_24_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2231,17 +2231,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>gallbladder_anatomy_quiz_form_section_23_choices</t>
+          <t>gallbladder_anatomy_quiz_form_section_24_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>stricture</t>
+          <t>obstruction</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Stricture</t>
+          <t>Obstruction</t>
         </is>
       </c>
     </row>
@@ -2253,44 +2253,10 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ulcer</t>
+          <t>blockage</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
-        <is>
-          <t>Ulcer</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>gallbladder_anatomy_quiz_form_section_24_choices</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>obstruction</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Obstruction</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>gallbladder_anatomy_quiz_form_section_24_choices</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>blockage</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
         <is>
           <t>Blockage</t>
         </is>
